--- a/results/log_pv_cap_per_inst_fit/log_pv_cap_per_inst_fit_densities_hdensity_estimates.xlsx
+++ b/results/log_pv_cap_per_inst_fit/log_pv_cap_per_inst_fit_densities_hdensity_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>densities-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_cap_per_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_cap_per_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_cap_per_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-queen-Running PooledOLS:queen for log_pv_cap_per_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_cap_per_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_cap_per_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-queen-Running PanelRE:queen for log_pv_cap_per_inst_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hdensity</t>
+          <t>D(Households)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>0.000*</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.000***</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.000***</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-0.000***</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.152***</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.084***</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.084***</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.084***</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.146***</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.146***</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.146***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -704,36 +614,6 @@
         </is>
       </c>
       <c r="J4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-0.002+</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-0.002+</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-0.002+</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
         <is>
           <t>-0.000</t>
         </is>
@@ -742,7 +622,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -788,126 +668,96 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>-0.047***</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-0.103***</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-0.103***</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-0.103***</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.052***</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.052***</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.052***</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_hdensity</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.005*</t>
+          <t>0.627***</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.001*</t>
+          <t>0.194***</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.001*</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>0.120***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.611***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.230***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.134***</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_income</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>-0.025</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.046+</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.045*</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.721***</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.207***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.121***</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
+          <t>W(D(Households))</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>-0.005*</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.002+</t>
+          <t>-0.001*</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>-0.001*</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -916,32 +766,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-0.025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>0.046+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.028*</t>
+          <t>0.045*</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -950,891 +794,320 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_log_pv_cap_per_inst_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.627***</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.194***</t>
+          <t>0.002+</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.120***</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.611***</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.230***</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.134***</t>
-        </is>
-      </c>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.017</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.210</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.210</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.220</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.208</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.205</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.191</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.192</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.192</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.052</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.052</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.052</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
+          <t>-0.028*</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-14749.163</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-14714.490</t>
+          <t>0.210</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-14714.961</t>
+          <t>0.210</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-14747.036</t>
+          <t>0.220</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-14712.173</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-14709.428</t>
+          <t>0.205</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-14746.989</t>
+          <t>0.191</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-14705.580</t>
+          <t>0.192</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14704.869</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>-7646.756</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-7646.756</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>-7646.756</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-7531.247</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>-7531.247</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>-7531.247</t>
+          <t>0.192</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-14698.419</t>
+          <t>-14749.163</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-14663.746</t>
+          <t>-14714.490</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-14664.217</t>
+          <t>-14714.961</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-14718.845</t>
+          <t>-14747.036</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-14683.982</t>
+          <t>-14712.173</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-14681.237</t>
+          <t>-14709.428</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-14724.437</t>
+          <t>-14746.989</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-14683.027</t>
+          <t>-14705.580</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-14682.316</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>-7618.565</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-7618.565</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>-7618.565</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-7503.056</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>-7503.056</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>-7503.056</t>
+          <t>-14704.869</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7383.581</t>
+          <t>-14698.419</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7366.245</t>
+          <t>-14663.746</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7366.480</t>
+          <t>-14664.217</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7378.518</t>
+          <t>-14718.845</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7361.087</t>
+          <t>-14683.982</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7359.714</t>
+          <t>-14681.237</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7377.495</t>
+          <t>-14724.437</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7356.790</t>
+          <t>-14683.027</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>7356.434</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>3828.378</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>3828.378</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>3828.378</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>3770.623</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>3770.623</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>3770.623</t>
+          <t>-14682.316</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7383.581</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7366.245</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7366.480</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7378.518</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7361.087</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7359.714</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7377.495</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>7356.790</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>7356.434</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df   p-value
-0       LM Marginal RE (LM1)    68.745192   1  0.000000
-1  LM Marginal Spatial (LM2)    -0.198727   1  0.578762
-2             LM Joint (LMJ)  4725.901445   2  0.000000</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df   p-value
-0       LM Marginal RE (LM1)    68.745192   1  0.000000
-1  LM Marginal Spatial (LM2)    -2.232640   1  0.987214
-2             LM Joint (LMJ)  4725.901445   2  0.000000</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df   p-value
-0       LM Marginal RE (LM1)    68.745192   1  0.000000
-1  LM Marginal Spatial (LM2)    -3.732362   1  0.999905
-2             LM Joint (LMJ)  4725.901445   2  0.000000</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df p-value
-0      LM Conditional Spatial  13.502475  1     0.0
-1  Hausman Specification Test  35.531748  4     0.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df   p-value
-0      LM Conditional Spatial   4.183262  1  0.000014
-1  Hausman Specification Test  35.531748  4       0.0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test  Statistic df p-value
-0      LM Conditional Spatial    5.09557  1     0.0
-1  Hausman Specification Test  35.531748  4     0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                   hdensity     0.000594    0.0002  2.973124  0.002948
-1                 log_income     0.096601  0.022376  4.317123  0.000016
-2                 log_hholds    -0.000365   0.00037 -0.986065  0.324101
-3            log_sunny_hours    -0.041911    0.0105 -3.991592  0.000066
-4                 W_hdensity    -0.004945  0.002203 -2.244803  0.024781
-5               W_log_income    -0.024908  0.033215 -0.749902  0.453314
-6               W_log_hholds     0.007007  0.006378  1.098667  0.271913
-7          W_log_sunny_hours      0.01659  0.015946  1.040394  0.298157
-8  W_log_pv_cap_per_inst_fit     0.627349  0.091532  6.853875       0.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                   hdensity      0.00047    0.0002   2.35355  0.018595
-1                 log_income     0.091425  0.021464  4.259475   0.00002
-2                 log_hholds    -0.000439  0.000373 -1.178131  0.238745
-3            log_sunny_hours    -0.041737  0.010016 -4.167109  0.000031
-4                 W_hdensity    -0.001209  0.000544 -2.222523  0.026248
-5               W_log_income     0.045858  0.024121  1.901143  0.057283
-6               W_log_hholds     0.001927  0.001113  1.730882  0.083473
-7          W_log_sunny_hours    -0.009688  0.013127 -0.738047  0.460486
-8  W_log_pv_cap_per_inst_fit      0.19426  0.041425   4.68944  0.000003</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                   hdensity      0.00047    0.0002  2.354209  0.018562
-1                 log_income     0.101856  0.020404  4.992003  0.000001
-2                 log_hholds    -0.000495  0.000373 -1.326273  0.184749
-3            log_sunny_hours    -0.032747  0.009781 -3.347925  0.000814
-4                 W_hdensity    -0.000668  0.000337 -1.980445  0.047654
-5               W_log_income     0.044697  0.021652  2.064357  0.038984
-6               W_log_hholds     0.000637  0.000625  1.019535  0.307949
-7          W_log_sunny_hours    -0.028265  0.012187  -2.31922  0.020383
-8  W_log_pv_cap_per_inst_fit     0.119619  0.032096  3.726879  0.000194</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err   zt_stat      prob
-0                   hdensity     0.000524  0.000198  2.643583  0.008203
-1                 log_income     0.073818  0.013179  5.601299       0.0
-2                 log_hholds    -0.000437   0.00037 -1.180042  0.237983
-3            log_sunny_hours    -0.034384  0.007588  -4.53141  0.000006
-4  W_log_pv_cap_per_inst_fit     0.610894  0.068659  8.897543       0.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err    zt_stat      prob
-0                   hdensity     0.000459    0.0002   2.298495  0.021534
-1                 log_income     0.124911  0.008954  13.951062       0.0
-2                 log_hholds    -0.000458  0.000373  -1.228587  0.219227
-3            log_sunny_hours    -0.044063  0.007211  -6.110564       0.0
-4  W_log_pv_cap_per_inst_fit     0.230164  0.038318   6.006733       0.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   var_names coefficients   std_err    zt_stat      prob
-0                   hdensity     0.000458    0.0002   2.292012  0.021905
-1                 log_income     0.135348  0.008389  16.133952       0.0
-2                 log_hholds    -0.000472  0.000374  -1.264653  0.205996
-3            log_sunny_hours    -0.045735  0.007196  -6.355409       0.0
-4  W_log_pv_cap_per_inst_fit     0.134118  0.030817   4.352092  0.000013</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err   zt_stat      prob
-0         hdensity     0.000596    0.0002  2.981503  0.002868
-1       log_income      0.13223  0.016835  7.854409       0.0
-2       log_hholds      -0.0004  0.000369 -1.082902  0.278852
-3  log_sunny_hours     -0.04049  0.009982 -4.056068   0.00005
-4           lambda     0.721402  0.072716   9.92084       0.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err   zt_stat      prob
-0         hdensity     0.000493  0.000201  2.456103  0.014045
-1       log_income     0.152848   0.00873  17.50833       0.0
-2       log_hholds    -0.000492  0.000372 -1.321683  0.186274
-3  log_sunny_hours    -0.046877  0.007987 -5.869339       0.0
-4           lambda     0.207271  0.041099  5.043187       0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         hdensity     0.000488  0.000201   2.430679  0.015071
-1       log_income     0.152189  0.008067  18.865557       0.0
-2       log_hholds    -0.000497  0.000373  -1.333398  0.182401
-3  log_sunny_hours    -0.046756  0.007654   -6.10904       0.0
-4           lambda     0.121311  0.032113   3.777595  0.000158</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.629954  0.060365  10.435806       0.0
-1         hdensity    -0.000438  0.000097  -4.515628  0.000007
-2       log_income     0.083895  0.009046   9.274006       0.0
-3       log_hholds    -0.001892  0.001038  -1.822707  0.068492
-4  log_sunny_hours    -0.103264  0.018392  -5.614745       0.0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.629954  0.060365  10.435806       0.0
-1         hdensity    -0.000438  0.000097  -4.515628  0.000007
-2       log_income     0.083895  0.009046   9.274006       0.0
-3       log_hholds    -0.001892  0.001038  -1.822707  0.068492
-4  log_sunny_hours    -0.103264  0.018392  -5.614745       0.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.629954  0.060365  10.435806       0.0
-1         hdensity    -0.000438  0.000097  -4.515628  0.000007
-2       log_income     0.083895  0.009046   9.274006       0.0
-3       log_hholds    -0.001892  0.001038  -1.822707  0.068492
-4  log_sunny_hours    -0.103264  0.018392  -5.614745       0.0</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.187635  0.036142   5.191612       0.0
-1         hdensity    -0.000132  0.000158   -0.83574  0.403301
-2       log_income     0.146477  0.007545  19.414336       0.0
-3       log_hholds    -0.000203  0.000407  -0.498366  0.618226
-4  log_sunny_hours    -0.051908  0.007856  -6.607094       0.0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.187635  0.036142   5.191612       0.0
-1         hdensity    -0.000132  0.000158   -0.83574  0.403301
-2       log_income     0.146477  0.007545  19.414336       0.0
-3       log_hholds    -0.000203  0.000407  -0.498366  0.618226
-4  log_sunny_hours    -0.051908  0.007856  -6.607094       0.0</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     0.187635  0.036142   5.191612       0.0
-1         hdensity    -0.000132  0.000158   -0.83574  0.403301
-2       log_income     0.146477  0.007545  19.414336       0.0
-3       log_hholds    -0.000203  0.000407  -0.498366  0.618226
-4  log_sunny_hours    -0.051908  0.007856  -6.607094       0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-hdensity                                    -0.011675   
-log_income                                   0.192385   
-log_hholds                                   0.017825   
-log_sunny_hours                             -0.067949   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-hdensity                                      0.000594   
-log_income                                    0.096601   
-log_hholds                                   -0.000365   
-log_sunny_hours                              -0.041911   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-hdensity                                       -0.012270  
-log_income                                      0.095784  
-log_hholds                                      0.018190  
-log_sunny_hours                                -0.026038  </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-hdensity                             -0.000917   
-log_income                            0.170381   
-log_hholds                            0.001846   
-log_sunny_hours                      -0.063824   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-hdensity                               0.000470   
-log_income                             0.091425   
-log_hholds                            -0.000439   
-log_sunny_hours                       -0.041737   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-hdensity                                -0.001387  
-log_income                               0.078956  
-log_hholds                               0.002286  
-log_sunny_hours                         -0.022087  </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-hdensity                         -0.000225                    0.000470   
-log_income                        0.166465                    0.101856   
-log_hholds                        0.000162                   -0.000495   
-log_sunny_hours                  -0.069301                   -0.032747   
-                 indirect_ML_LagFE(SLX)_queen  
-hdensity                            -0.000695  
-log_income                           0.064609  
-log_hholds                           0.000657  
-log_sunny_hours                     -0.036554  </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-hdensity                                0.001347   
-log_income                              0.189712   
-log_hholds                             -0.001123   
-log_sunny_hours                        -0.088366   
-                 direct_ML_LagFE_inverse_distance  \
-hdensity                                 0.000524   
-log_income                               0.073818   
-log_hholds                              -0.000437   
-log_sunny_hours                         -0.034384   
-                 indirect_ML_LagFE_inverse_distance  
-hdensity                                   0.000823  
-log_income                                 0.115894  
-log_hholds                                -0.000686  
-log_sunny_hours                           -0.053982  </t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-hdensity                         0.000596                   0.000459   
-log_income                       0.162257                   0.124911   
-log_hholds                      -0.000595                  -0.000458   
-log_sunny_hours                 -0.057237                  -0.044063   
-                 indirect_ML_LagFE_k_nearest  
-hdensity                            0.000137  
-log_income                          0.037346  
-log_hholds                         -0.000137  
-log_sunny_hours                    -0.013174  </t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-hdensity                     0.000529               0.000458   
-log_income                   0.156312               0.135348   
-log_hholds                  -0.000546              -0.000472   
-log_sunny_hours             -0.052819              -0.045735   
-                 indirect_ML_LagFE_queen  
-hdensity                        0.000071  
-log_income                      0.020964  
-log_hholds                     -0.000073  
-log_sunny_hours                -0.007084  </t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.721***</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.207***</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.121***</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.630***</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0.630***</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>0.630***</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>0.188***</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>0.188***</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>0.188***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
